--- a/data/trans_orig/Q5404-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5404-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de manejar dinero en 2007</t>
+          <t>Población según si es capaz de manejar dinero en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16012</t>
+          <t>15257</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17453</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38299</t>
+          <t>39160</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25738</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49981</t>
+          <t>48550</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11698</t>
+          <t>11699</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27134</t>
+          <t>26461</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22713</t>
+          <t>22567</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45385</t>
+          <t>45035</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38878</t>
+          <t>39416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65442</t>
+          <t>65748</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>334623</t>
+          <t>335788</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>354332</t>
+          <t>354901</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>513689</t>
+          <t>510428</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>541674</t>
+          <t>542945</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>855841</t>
+          <t>855096</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>890807</t>
+          <t>889525</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>914</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>847</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77635</t>
+          <t>76463</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86482</t>
+          <t>86484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53598</t>
+          <t>53434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61303</t>
+          <t>61287</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135259</t>
+          <t>134532</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147358</t>
+          <t>146987</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1758,97 +1758,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41194</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>19218</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19218</t>
+          <t>19259</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41045</t>
+          <t>40464</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27873</t>
+          <t>28782</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53769</t>
+          <t>55118</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13916</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31602</t>
+          <t>29910</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24032</t>
+          <t>24356</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47431</t>
+          <t>47509</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41916</t>
+          <t>42763</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69174</t>
+          <t>70900</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>457783</t>
+          <t>459469</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>480232</t>
+          <t>480326</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>597619</t>
+          <t>597520</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>627669</t>
+          <t>628825</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1064244</t>
+          <t>1062788</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1102137</t>
+          <t>1102062</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de manejar dinero en 2012</t>
+          <t>Población según si es capaz de manejar dinero en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14278</t>
+          <t>13847</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32573</t>
+          <t>33667</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31382</t>
+          <t>31213</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57126</t>
+          <t>57613</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48314</t>
+          <t>49276</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80026</t>
+          <t>81710</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15168</t>
+          <t>15964</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36888</t>
+          <t>36762</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57044</t>
+          <t>57708</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90941</t>
+          <t>89530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79687</t>
+          <t>80458</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118237</t>
+          <t>117609</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>351888</t>
+          <t>351794</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>379377</t>
+          <t>380659</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>497811</t>
+          <t>497482</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>539816</t>
+          <t>538265</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>860782</t>
+          <t>862772</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>911290</t>
+          <t>909668</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,72%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13679</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16320</t>
+          <t>15360</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103890</t>
+          <t>102224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116516</t>
+          <t>116535</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73390</t>
+          <t>73931</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82018</t>
+          <t>83074</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>182654</t>
+          <t>183219</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197336</t>
+          <t>197368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -3700,97 +3700,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2222</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2331</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3813,97 +3813,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5753</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>25,86%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5031</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5529</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>22,61%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4900</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24279</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17215</t>
+          <t>16493</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43921</t>
+          <t>43292</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35101</t>
+          <t>33816</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32721</t>
+          <t>32300</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61144</t>
+          <t>59435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53234</t>
+          <t>51884</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86407</t>
+          <t>84692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>19699</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45463</t>
+          <t>44532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58966</t>
+          <t>58512</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93266</t>
+          <t>92137</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84912</t>
+          <t>85810</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>126345</t>
+          <t>128288</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>488260</t>
+          <t>490400</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>519724</t>
+          <t>520596</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>597230</t>
+          <t>597624</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>640863</t>
+          <t>639645</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1103061</t>
+          <t>1100821</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1151121</t>
+          <t>1153929</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,8%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de manejar dinero en 2016</t>
+          <t>Población según si es capaz de manejar dinero en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15111</t>
+          <t>15473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14612</t>
+          <t>15154</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37175</t>
+          <t>38373</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>22546</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46258</t>
+          <t>47553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11602</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27081</t>
+          <t>26789</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27869</t>
+          <t>27001</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54596</t>
+          <t>54418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44647</t>
+          <t>44224</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75125</t>
+          <t>76275</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>317217</t>
+          <t>317149</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>335291</t>
+          <t>335069</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>472995</t>
+          <t>472380</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>506151</t>
+          <t>506324</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>798613</t>
+          <t>797083</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>835860</t>
+          <t>836335</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13026</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15802</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15769</t>
+          <t>15002</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18265</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>184885</t>
+          <t>184397</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191781</t>
+          <t>191622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>165133</t>
+          <t>164595</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>181731</t>
+          <t>182454</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>352955</t>
+          <t>353459</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>372281</t>
+          <t>371661</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -5755,97 +5755,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>37671</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67356</t>
+          <t>67887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17047</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19099</t>
+          <t>18521</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44082</t>
+          <t>42385</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26682</t>
+          <t>27019</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54487</t>
+          <t>54485</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>13677</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30757</t>
+          <t>30169</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35969</t>
+          <t>35585</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66145</t>
+          <t>66994</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53183</t>
+          <t>53339</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87628</t>
+          <t>87697</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>546256</t>
+          <t>546642</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>566039</t>
+          <t>566419</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>677199</t>
+          <t>678193</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>716145</t>
+          <t>715127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1231820</t>
+          <t>1235006</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1276555</t>
+          <t>1275457</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de manejar dinero en 2023</t>
+          <t>Población según si es capaz de manejar dinero en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27865</t>
+          <t>26818</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44823</t>
+          <t>44638</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33700</t>
+          <t>34204</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53474</t>
+          <t>53246</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>13730</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27691</t>
+          <t>28499</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48487</t>
+          <t>47542</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68691</t>
+          <t>68295</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65749</t>
+          <t>65730</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>91251</t>
+          <t>90762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>233952</t>
+          <t>233961</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>250103</t>
+          <t>249839</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>392940</t>
+          <t>392832</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>417795</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>632867</t>
+          <t>632903</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>663158</t>
+          <t>662836</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,15%</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>337</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>7778</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30643</t>
+          <t>30093</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9887</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38049</t>
+          <t>37890</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>255247</t>
+          <t>256450</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>266703</t>
+          <t>266810</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>420456</t>
+          <t>421082</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>449982</t>
+          <t>449892</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>686520</t>
+          <t>685640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>717557</t>
+          <t>716570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -7810,97 +7810,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>764</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>559</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98600</t>
+          <t>98438</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104203</t>
+          <t>104222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65821</t>
+          <t>66629</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70725</t>
+          <t>70766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>166914</t>
+          <t>167417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>174327</t>
+          <t>174104</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>13992</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17932</t>
+          <t>18156</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51675</t>
+          <t>52412</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30468</t>
+          <t>29690</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58887</t>
+          <t>58548</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22614</t>
+          <t>23818</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41022</t>
+          <t>41347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37605</t>
+          <t>41042</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96928</t>
+          <t>99925</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70020</t>
+          <t>72808</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>128068</t>
+          <t>128476</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>596411</t>
+          <t>597224</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>616739</t>
+          <t>616489</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>882569</t>
+          <t>879128</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>970829</t>
+          <t>966559</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1493174</t>
+          <t>1493666</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1569058</t>
+          <t>1577177</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5404-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5404-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15257</t>
+          <t>15937</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17430</t>
+          <t>17326</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39160</t>
+          <t>39351</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24779</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48550</t>
+          <t>49834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11699</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26461</t>
+          <t>27494</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22567</t>
+          <t>22673</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45035</t>
+          <t>45721</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39416</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65748</t>
+          <t>65437</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>335788</t>
+          <t>335228</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>354901</t>
+          <t>354163</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>510428</t>
+          <t>511828</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>542945</t>
+          <t>541797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>855096</t>
+          <t>854994</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>889525</t>
+          <t>890641</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>930</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>808</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>7436</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8425</t>
+          <t>10332</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76463</t>
+          <t>76941</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86484</t>
+          <t>86468</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53434</t>
+          <t>53743</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61287</t>
+          <t>61307</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134532</t>
+          <t>134657</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146987</t>
+          <t>147184</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19218</t>
+          <t>18854</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19259</t>
+          <t>19584</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40464</t>
+          <t>40052</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28782</t>
+          <t>28488</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55118</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29910</t>
+          <t>31579</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24356</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47509</t>
+          <t>46644</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42763</t>
+          <t>41076</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70900</t>
+          <t>70642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>459469</t>
+          <t>458962</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>480326</t>
+          <t>479663</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>597520</t>
+          <t>598847</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>628825</t>
+          <t>628560</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1062788</t>
+          <t>1066793</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1102062</t>
+          <t>1104239</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13847</t>
+          <t>13829</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33667</t>
+          <t>33693</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31213</t>
+          <t>30038</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57613</t>
+          <t>56635</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49276</t>
+          <t>49663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81710</t>
+          <t>82158</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15964</t>
+          <t>15930</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36762</t>
+          <t>37045</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57708</t>
+          <t>58959</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89530</t>
+          <t>91393</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80458</t>
+          <t>77786</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117609</t>
+          <t>117962</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>351794</t>
+          <t>353067</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>380659</t>
+          <t>379179</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>497482</t>
+          <t>499496</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>538265</t>
+          <t>538353</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>862772</t>
+          <t>860250</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>909668</t>
+          <t>910775</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>15376</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15360</t>
+          <t>15906</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102224</t>
+          <t>103551</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116535</t>
+          <t>116573</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73931</t>
+          <t>73833</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83074</t>
+          <t>82028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183219</t>
+          <t>181777</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197368</t>
+          <t>197379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16493</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43292</t>
+          <t>43035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33816</t>
+          <t>36255</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32300</t>
+          <t>32906</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59435</t>
+          <t>60242</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51884</t>
+          <t>53010</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84692</t>
+          <t>87232</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>18926</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44532</t>
+          <t>43883</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58512</t>
+          <t>59003</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92137</t>
+          <t>94184</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85810</t>
+          <t>84954</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>128288</t>
+          <t>126181</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>490400</t>
+          <t>488971</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>520596</t>
+          <t>520483</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>597624</t>
+          <t>597130</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>639645</t>
+          <t>639035</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1100821</t>
+          <t>1098171</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1153929</t>
+          <t>1151318</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,6%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15473</t>
+          <t>15752</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15154</t>
+          <t>15411</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38373</t>
+          <t>39708</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22546</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47553</t>
+          <t>47084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26789</t>
+          <t>28090</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27001</t>
+          <t>27506</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54418</t>
+          <t>53871</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44224</t>
+          <t>43541</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76275</t>
+          <t>74821</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>317149</t>
+          <t>315812</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>335069</t>
+          <t>334870</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>472380</t>
+          <t>471492</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>506324</t>
+          <t>505857</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>797083</t>
+          <t>796658</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>836335</t>
+          <t>835403</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>16428</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>15905</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15002</t>
+          <t>14877</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>17143</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>184397</t>
+          <t>184601</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191622</t>
+          <t>191653</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>164595</t>
+          <t>166241</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>182454</t>
+          <t>182014</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>353459</t>
+          <t>354219</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>371661</t>
+          <t>372255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7816</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37671</t>
+          <t>37576</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67887</t>
+          <t>67683</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>17322</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18521</t>
+          <t>18995</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42385</t>
+          <t>43983</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27019</t>
+          <t>27872</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54485</t>
+          <t>55926</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13677</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30169</t>
+          <t>29073</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35585</t>
+          <t>35991</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66994</t>
+          <t>64604</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53339</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87697</t>
+          <t>89539</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>546642</t>
+          <t>547022</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>566419</t>
+          <t>567361</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>678193</t>
+          <t>679593</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>715127</t>
+          <t>715638</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1235006</t>
+          <t>1235063</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1275457</t>
+          <t>1276471</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>12595</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>35683</t>
+          <t>38642</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26818</t>
+          <t>29599</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44638</t>
+          <t>49015</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>42732</t>
+          <t>45862</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34204</t>
+          <t>36751</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53246</t>
+          <t>57124</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19615</t>
+          <t>20879</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>13715</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28499</t>
+          <t>29801</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57840</t>
+          <t>61955</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47542</t>
+          <t>51760</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68295</t>
+          <t>73046</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>77454</t>
+          <t>82834</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65730</t>
+          <t>70262</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90762</t>
+          <t>97340</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>242581</t>
+          <t>261996</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>233961</t>
+          <t>252306</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>249839</t>
+          <t>269827</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>406617</t>
+          <t>437538</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>392832</t>
+          <t>423405</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>450861</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>649198</t>
+          <t>699535</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>632903</t>
+          <t>683767</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>662836</t>
+          <t>714108</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,22%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>500140</t>
+          <t>538135</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>500140</t>
+          <t>538135</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>500140</t>
+          <t>538135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>769384</t>
+          <t>828230</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>769384</t>
+          <t>828230</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>769384</t>
+          <t>828230</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9976</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15135</t>
+          <t>16114</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14832</t>
+          <t>17021</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>12176</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30093</t>
+          <t>23983</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>24355</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>20343</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37890</t>
+          <t>35965</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>262388</t>
+          <t>292592</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>256450</t>
+          <t>285888</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>266810</t>
+          <t>296976</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>438660</t>
+          <t>258282</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>421082</t>
+          <t>251441</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>449892</t>
+          <t>263418</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>701049</t>
+          <t>550874</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>685640</t>
+          <t>541159</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>716570</t>
+          <t>557799</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7918,27 +7918,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -8031,22 +8031,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>102542</t>
+          <t>115494</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98438</t>
+          <t>111463</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104222</t>
+          <t>117714</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>69141</t>
+          <t>80447</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66629</t>
+          <t>77170</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70766</t>
+          <t>82234</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>171683</t>
+          <t>195941</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>167417</t>
+          <t>191122</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>174104</t>
+          <t>198941</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13992</t>
+          <t>13966</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>37930</t>
+          <t>40984</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18156</t>
+          <t>31839</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52412</t>
+          <t>51554</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>46324</t>
+          <t>49461</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>39025</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58548</t>
+          <t>61561</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31582</t>
+          <t>34241</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23818</t>
+          <t>25118</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41347</t>
+          <t>44708</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>74856</t>
+          <t>81385</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41042</t>
+          <t>70207</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99925</t>
+          <t>94717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>106438</t>
+          <t>115626</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72808</t>
+          <t>100401</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>128476</t>
+          <t>133235</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>607511</t>
+          <t>670082</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>597224</t>
+          <t>658123</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>616489</t>
+          <t>679422</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>914419</t>
+          <t>776267</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>879128</t>
+          <t>760872</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>966559</t>
+          <t>791687</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1521929</t>
+          <t>1446351</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1493666</t>
+          <t>1426457</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1577177</t>
+          <t>1464501</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
+          <t>89,76%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>88,52%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
           <t>90,88%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>89,19%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1027204</t>
+          <t>898636</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1027204</t>
+          <t>898636</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1027204</t>
+          <t>898636</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1674691</t>
+          <t>1611438</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1674691</t>
+          <t>1611438</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1674691</t>
+          <t>1611438</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
